--- a/data/dividends_info_20260813.xlsx
+++ b/data/dividends_info_20260813.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.72000122070312</v>
+        <v>47.66500091552734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1886001628201004</v>
+        <v>0.1888177872051223</v>
       </c>
       <c r="J2" t="n">
         <v>214</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>68.05000305175781</v>
+        <v>66.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.028655354309963</v>
+        <v>1.048689138576779</v>
       </c>
       <c r="J3" t="n">
         <v>193</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.439999580383301</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6355932485916886</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>123</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4939999878406525</v>
+        <v>0.4979999959468842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8097166191206999</v>
+        <v>0.8032128579428007</v>
       </c>
       <c r="J5" t="n">
         <v>123</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.72000122070312</v>
+        <v>47.66500091552734</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1886001628201004</v>
+        <v>0.1888177872051223</v>
       </c>
       <c r="J6" t="n">
         <v>123</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.66500091552734</v>
+        <v>23.70499992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.140925373143952</v>
+        <v>1.139000214591809</v>
       </c>
       <c r="J8" t="n">
         <v>102</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.02000045776367</v>
+        <v>23.03000068664551</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56298865450725</v>
+        <v>2.56187573777245</v>
       </c>
       <c r="J9" t="n">
         <v>102</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.889999866485596</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I10" t="n">
-        <v>3.395585815510971</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J10" t="n">
         <v>95</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.56999969482422</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="I11" t="n">
-        <v>4.351939576925881</v>
+        <v>4.299065497194548</v>
       </c>
       <c r="J11" t="n">
         <v>74</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.5</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J12" t="n">
         <v>67</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4979999959468842</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8032128579428007</v>
       </c>
       <c r="J13" t="n">
         <v>67</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.599999904632568</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8928571580624097</v>
+        <v>0.8620689371678274</v>
       </c>
       <c r="J14" t="n">
         <v>53</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.66500091552734</v>
+        <v>23.70499992370605</v>
       </c>
       <c r="I16" t="n">
-        <v>1.140925373143952</v>
+        <v>1.139000214591809</v>
       </c>
       <c r="J16" t="n">
         <v>39</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.968999981880188</v>
+        <v>1.965000033378601</v>
       </c>
       <c r="I17" t="n">
-        <v>2.894870519276033</v>
+        <v>2.90076330950462</v>
       </c>
       <c r="J17" t="n">
         <v>39</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>47.72000122070312</v>
+        <v>47.66500091552734</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1886001628201004</v>
+        <v>0.1888177872051223</v>
       </c>
       <c r="J18" t="n">
         <v>39</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.59999847412109</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.405919684410816</v>
+        <v>1.417155057670826</v>
       </c>
       <c r="J19" t="n">
         <v>39</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4979999959468842</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8032128579428007</v>
       </c>
       <c r="J21" t="n">
         <v>11</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.700000047683716</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I22" t="n">
-        <v>8.148148004246677</v>
+        <v>8.20895501940042</v>
       </c>
       <c r="J22" t="n">
         <v>-3</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.640000104904175</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>5.604886140918198</v>
+        <v>5.647672002414033</v>
       </c>
       <c r="J25" t="n">
         <v>-10</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6.019999980926514</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I26" t="n">
-        <v>4.152823933423394</v>
+        <v>4.159733618621054</v>
       </c>
       <c r="J26" t="n">
         <v>-17</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.230000019073486</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="I27" t="n">
-        <v>3.30969265647107</v>
+        <v>3.325415646827901</v>
       </c>
       <c r="J27" t="n">
         <v>-24</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.692000389099121</v>
+        <v>9.689000129699707</v>
       </c>
       <c r="I28" t="n">
-        <v>2.682624737535397</v>
+        <v>2.683455429038768</v>
       </c>
       <c r="J28" t="n">
         <v>-24</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.80000019073486</v>
+        <v>13.68000030517578</v>
       </c>
       <c r="I29" t="n">
-        <v>4.347826026863623</v>
+        <v>4.385964814437847</v>
       </c>
       <c r="J29" t="n">
         <v>-24</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.665999889373779</v>
+        <v>2.681999921798706</v>
       </c>
       <c r="I30" t="n">
-        <v>8.252063358175011</v>
+        <v>8.20283394536623</v>
       </c>
       <c r="J30" t="n">
         <v>-24</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4979999959468842</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8032128579428007</v>
       </c>
       <c r="J31" t="n">
         <v>-24</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.5</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I32" t="n">
-        <v>3.692307692307692</v>
+        <v>3.609022504634104</v>
       </c>
       <c r="J32" t="n">
         <v>-24</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.89999961853027</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I33" t="n">
-        <v>1.989418029571574</v>
+        <v>2.000000081163775</v>
       </c>
       <c r="J33" t="n">
         <v>-24</v>
